--- a/数值知识库-网页版GPT/源表/X-systemConfiguration-系统配置表.xlsx
+++ b/数值知识库-网页版GPT/源表/X-systemConfiguration-系统配置表.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UGit\sldh-config\Config\Excels\Tables\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3F558373-D861-41F1-9550-B20D0301283D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{385AB921-12FD-408F-9B65-3621E83EA3DC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="110" uniqueCount="107">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="110">
   <si>
     <t>##var</t>
   </si>
@@ -799,162 +799,171 @@
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
   <si>
+    <t>账号初始体力</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>体力自然恢复上限</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>广告补充体力的数量（体力道具ID:数量）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>210009:3</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日看广告补充的次数限制(次数)</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>每日重置时间（24小时制：5代表凌晨5点。）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>恢复1点体力所需的时间（秒）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>默认钩锁绑定伤害（hurt）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>用户名字符长度：</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color rgb="FF000000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>用户名的最大字数</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>（中文|繁体|英语|日文|韩文）</t>
+    </r>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>7|7|14|7|7</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>商店刷新：每日免费次数（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <r>
+      <t>商店刷新：刷新消耗货币（</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FFC00000"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>测试</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color rgb="FF00B050"/>
+        <rFont val="微软雅黑"/>
+        <family val="2"/>
+        <charset val="134"/>
+      </rPr>
+      <t>）</t>
+    </r>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>首充：解锁需要的通关关卡ID</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>首充：已购买后登录是否自动弹出（0=已购买后永不弹出（仅依靠红点提示））</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>首充：未购买时首次登录是否自动弹出（1=未购买时登录弹出）</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>210008:1</t>
+  </si>
+  <si>
+    <t>210008:10</t>
+  </si>
+  <si>
+    <t>抽卡综合概率公示（含保底，整数百分比约数：1=1%）</t>
+  </si>
+  <si>
+    <t>310000:13|310001:13|310002:13|310003:2|310004:2|310005:1|310006:1|310008:1|310009:2|310011:2|210001:17|110001:11|110002:11|110003:11</t>
+  </si>
+  <si>
+    <t>600</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>25:210001:10|50:210002:20|75:210010:30|100:210002:40</t>
+    <phoneticPr fontId="12" type="noConversion"/>
+  </si>
+  <si>
+    <t>10:10:10:10:10:10:10:10:10:10:10:10</t>
+  </si>
+  <si>
+    <t>怪物环境伤害最大生命值百分比（顺序同配置65）</t>
+  </si>
+  <si>
     <t>30:30:30:30:30:30:30:30:30:30:30:30</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>账号初始体力</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>体力自然恢复上限</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>广告补充体力的数量（体力道具ID:数量）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>210009:3</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>每日看广告补充的次数限制(次数)</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>每日重置时间（24小时制：5代表凌晨5点。）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>恢复1点体力所需的时间（秒）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>默认钩锁绑定伤害（hurt）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>用户名字符长度：</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color rgb="FF000000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>用户名的最大字数</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>（中文|繁体|英语|日文|韩文）</t>
-    </r>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>7|7|14|7|7</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>商店刷新：每日免费次数（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <r>
-      <t>商店刷新：刷新消耗货币（</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FFC00000"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>测试</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color rgb="FF00B050"/>
-        <rFont val="微软雅黑"/>
-        <family val="2"/>
-        <charset val="134"/>
-      </rPr>
-      <t>）</t>
-    </r>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100|210002:100</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>首充：解锁需要的通关关卡ID</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>首充：已购买后登录是否自动弹出（0=已购买后永不弹出（仅依靠红点提示））</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>首充：未购买时首次登录是否自动弹出（1=未购买时登录弹出）</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>210008:1</t>
-  </si>
-  <si>
-    <t>210008:10</t>
-  </si>
-  <si>
-    <t>抽卡综合概率公示（含保底，整数百分比约数：1=1%）</t>
-  </si>
-  <si>
-    <t>310000:13|310001:13|310002:13|310003:2|310004:2|310005:1|310006:1|310008:1|310009:2|310011:2|210001:17|110001:11|110002:11|110003:11</t>
-  </si>
-  <si>
-    <t>600</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>25:210001:10|50:210002:20|75:210010:30|100:210002:40</t>
+  </si>
+  <si>
+    <t>主线关卡死亡后可复活次数</t>
     <phoneticPr fontId="12" type="noConversion"/>
   </si>
 </sst>
@@ -962,7 +971,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1078,14 +1087,6 @@
       <charset val="134"/>
     </font>
     <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="9" tint="-0.249977111117893"/>
-      <name val="微软雅黑"/>
-      <family val="2"/>
-      <charset val="134"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1" tint="4.9989318521683403E-2"/>
       <name val="微软雅黑"/>
@@ -1191,7 +1192,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyBorder="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="0" applyBorder="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="30">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1268,7 +1269,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1276,15 +1276,9 @@
       <alignment horizontal="left"/>
     </xf>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="17" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="16" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1550,7 +1544,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z79"/>
+  <dimension ref="A1:Z78"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" customHeight="1" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="9.875" style="1" customWidth="1"/>
@@ -1784,10 +1778,10 @@
         <v>6</v>
       </c>
       <c r="C11" s="17" t="s">
+        <v>92</v>
+      </c>
+      <c r="D11" s="18" t="s">
         <v>93</v>
-      </c>
-      <c r="D11" s="18" t="s">
-        <v>94</v>
       </c>
     </row>
     <row r="12" spans="1:26" x14ac:dyDescent="0.3">
@@ -2148,7 +2142,7 @@
         <v>37</v>
       </c>
       <c r="C42" s="17" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D42" s="3">
         <v>5</v>
@@ -2162,7 +2156,7 @@
         <v>52</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -2280,7 +2274,7 @@
         <v>49</v>
       </c>
       <c r="C54" s="17" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D54" s="3">
         <v>1</v>
@@ -2302,10 +2296,10 @@
         <v>51</v>
       </c>
       <c r="C56" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>96</v>
-      </c>
-      <c r="D56" s="3" t="s">
-        <v>97</v>
       </c>
     </row>
     <row r="57" spans="2:4" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2393,7 +2387,7 @@
         <v>81</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="65" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2404,7 +2398,7 @@
         <v>82</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="66" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2412,10 +2406,10 @@
         <v>64</v>
       </c>
       <c r="C66" s="2" t="s">
+        <v>102</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>103</v>
-      </c>
-      <c r="D66" s="3" t="s">
-        <v>104</v>
       </c>
     </row>
     <row r="67" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2425,10 +2419,8 @@
       <c r="C67" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D67" s="3" t="inlineStr">
-        <is>
-          <t>10:10:10:10:10:10:10:10:10:10:10:10</t>
-        </is>
+      <c r="D67" s="3" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="68" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2436,9 +2428,9 @@
         <v>66</v>
       </c>
       <c r="C68" s="2" t="s">
-        <v>85</v>
-      </c>
-      <c r="D68" s="31">
+        <v>84</v>
+      </c>
+      <c r="D68" s="28">
         <v>10</v>
       </c>
     </row>
@@ -2447,9 +2439,9 @@
         <v>67</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>86</v>
-      </c>
-      <c r="D69" s="31">
+        <v>85</v>
+      </c>
+      <c r="D69" s="28">
         <v>10</v>
       </c>
     </row>
@@ -2458,10 +2450,10 @@
         <v>68</v>
       </c>
       <c r="C70" s="2" t="s">
-        <v>91</v>
-      </c>
-      <c r="D70" s="32" t="s">
-        <v>105</v>
+        <v>90</v>
+      </c>
+      <c r="D70" s="29" t="s">
+        <v>104</v>
       </c>
     </row>
     <row r="71" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2469,10 +2461,10 @@
         <v>70</v>
       </c>
       <c r="C71" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="D71" s="22" t="s">
         <v>87</v>
-      </c>
-      <c r="D71" s="22" t="s">
-        <v>88</v>
       </c>
     </row>
     <row r="72" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2480,7 +2472,7 @@
         <v>71</v>
       </c>
       <c r="C72" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D72" s="3">
         <v>3</v>
@@ -2491,7 +2483,7 @@
         <v>72</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D73" s="3">
         <v>999</v>
@@ -2502,9 +2494,9 @@
         <v>73</v>
       </c>
       <c r="C74" s="2" t="s">
-        <v>98</v>
-      </c>
-      <c r="D74" s="27">
+        <v>97</v>
+      </c>
+      <c r="D74" s="26">
         <v>1000040</v>
       </c>
     </row>
@@ -2513,12 +2505,12 @@
         <v>74</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D75" s="3">
         <v>1</v>
       </c>
-      <c r="E75" s="28"/>
+      <c r="E75" s="27"/>
       <c r="F75" s="2"/>
     </row>
     <row r="76" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
@@ -2526,40 +2518,38 @@
         <v>75</v>
       </c>
       <c r="C76" s="2" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D76" s="3">
         <v>0</v>
       </c>
-      <c r="E76" s="27"/>
+      <c r="E76" s="26"/>
       <c r="F76" s="2"/>
     </row>
     <row r="77" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B77" s="1">
         <v>76</v>
       </c>
-      <c r="C77" s="2" t="inlineStr">
-        <is>
-          <t>怪物环境伤害最大生命值百分比（顺序同配置65）</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>30:30:30:30:30:30:30:30:30:30:30:30</t>
-        </is>
+      <c r="C77" s="2" t="s">
+        <v>107</v>
+      </c>
+      <c r="D77" s="3" t="s">
+        <v>108</v>
       </c>
       <c r="E77" s="2"/>
       <c r="F77" s="2"/>
     </row>
     <row r="78" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C78" s="29"/>
-      <c r="D78" s="30"/>
-      <c r="E78" s="2"/>
+      <c r="B78" s="1">
+        <v>77</v>
+      </c>
+      <c r="C78" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="D78" s="3">
+        <v>1</v>
+      </c>
       <c r="F78" s="2"/>
-    </row>
-    <row r="79" spans="2:6" ht="16.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="C79" s="26"/>
-      <c r="F79" s="2"/>
     </row>
   </sheetData>
   <phoneticPr fontId="12" type="noConversion"/>
